--- a/tabular/refseq-core/ifnl-refseq-side-data.xlsx
+++ b/tabular/refseq-core/ifnl-refseq-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/host/IFNL-Evolution/tabular/refseq-core/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/host/IFNL-Evolution/tabular/refseq-core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B940E404-2EA1-6D47-AF65-0E429FD8F09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF303C9-C5A9-3642-90B9-F7C11DD277B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17680" yWindow="5960" windowWidth="28060" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A+B" sheetId="2" r:id="rId1"/>

--- a/tabular/refseq-core/ifnl-refseq-side-data.xlsx
+++ b/tabular/refseq-core/ifnl-refseq-side-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/host/IFNL-Evolution/tabular/refseq-core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF303C9-C5A9-3642-90B9-F7C11DD277B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D682C36-485E-104B-843A-E18262D77B5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -513,7 +513,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,12 +523,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF660066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9C8FE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,43 +540,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99FF66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBEA4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59996337778862885"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="0" tint="-0.14996795556505021"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1127,42 +1097,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1170,25 +1134,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="529">
@@ -2081,21 +2050,21 @@
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="21.33203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" style="18"/>
+    <col min="12" max="12" width="15.83203125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="13" t="s">
         <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -2119,390 +2088,390 @@
       <c r="K1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="21">
         <v>1</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="21">
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="21">
         <v>1</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="21">
         <v>1</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="21">
         <v>1</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="21">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="K7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="21">
         <v>1</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="21">
         <v>2</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="22" t="s">
+      <c r="K11" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M11">
@@ -2573,15 +2542,15 @@
       <c r="P1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2627,7 +2596,7 @@
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2677,7 +2646,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -2725,7 +2694,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2753,7 +2722,7 @@
         <v>2</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="13"/>
+      <c r="K5" s="10"/>
       <c r="L5" s="7">
         <v>2</v>
       </c>
